--- a/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Frasningskonsistens lärandemål" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens lärandemål'!$A$1:$E$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$304</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E204"/>
+  <dimension ref="A1:E304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,115 +472,115 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AIH237</t>
+          <t>AFT2C8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>FYS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - självständigt identifiera ett idrottsdidaktiskt problemområde och for…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AIH24T</t>
+          <t>AFT2C9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>FYS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - självständigt identifiera ett idrottsdidaktiskt problemområde och for…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GIH24A</t>
+          <t>AFT2CA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>FYS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - diskutera och analysera relationen mellan medierna och idrotten   - r…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH24A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2CA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GIH2A6</t>
+          <t>AFT2CB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>FYS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för och visa förståelse för centrala begrepp inom  idrottsps…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2CB</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GIH2D4</t>
+          <t>AIH237</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -590,24 +590,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för judons historia och värdegrund samt kunna applicera och…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GIH2D5</t>
+          <t>AIH24T</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -617,24 +617,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för generell teknik i tävlingsgodkända lyft i disciplinerna…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GIH2D6</t>
+          <t>GIH24A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -644,24 +644,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna redogöra för:    - nervsystemets och musklernas up…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH24A</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GIH2D7</t>
+          <t>GIH2A6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna redogöra för:    - nervsystemets och musklernas up…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2A6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GIH2D8</t>
+          <t>GIH2D4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -698,24 +698,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:    - reflektera över och diskutera tränarrollen u…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GIH2D9</t>
+          <t>GIH2D5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -725,24 +725,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:    - reflektera kring och diskutera tränarrollen…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GIH2DB</t>
+          <t>GIH2D6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -752,24 +752,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:    - redogöra för krafter, hävarmar och vridande…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna redogöra för:…</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GIH2DC</t>
+          <t>GIH2D7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -779,24 +779,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:    - redogöra för krafter, hävarmar och vridande…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna redogöra för:…</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GIH2DD</t>
+          <t>GIH2D8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -806,24 +806,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:    - redogöra för rörelseapparatens uppbyggnad oc…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GIH2DE</t>
+          <t>GIH2D9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -833,24 +833,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:    - redogöra för rörelseapparatens uppbyggnad oc…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GIH2G4</t>
+          <t>GIH2DB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -860,24 +860,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - hantera mätutrustning och olika metoder för rörelse- och prestationsa…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DB</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GIH2LP</t>
+          <t>GIH2DC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -887,24 +887,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för och analysera samhällsutvecklingen relaterat till friluf…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GIH2LT</t>
+          <t>GIH2DD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -914,24 +914,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna:     - visa förmåga att planera, leda och utvärdera träning som skapar fö…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GIH2LU</t>
+          <t>GIH2DE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -941,24 +941,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna:     - visa förmåga att planera, leda och utvärdera träning som skapar fö…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GIH2LV</t>
+          <t>GIH2G4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -968,24 +968,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - tillämpa grundläggande kunskaper inom ämnesområdena tränings- och täv…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GIH2LW</t>
+          <t>GIH2LP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -995,24 +995,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - tillämpa grundläggande kunskaper inom ämnesområdena tränings- och täv…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LP</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GIH2LX</t>
+          <t>GIH2LT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1022,24 +1022,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - tillämpa olika teorier om motoriskt lärande och kontroll inom judoträ…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GIH2LY</t>
+          <t>GIH2LU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1049,24 +1049,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - tillämpa olika teorier om motoriskt lärande och kontroll inom träning…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GIH2M4</t>
+          <t>GIH2LV</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:     - tillämpa olika teorier om motoriskt lärande och kontroll inom klättr…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GIH2M5</t>
+          <t>GIH2LW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1103,24 +1103,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - tillämpa grundläggande kunskaper inom ämnesområdena tränings- och täv…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GIH2M6</t>
+          <t>GIH2LX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - visa förmåga att planera, leda och utvärdera träning som skapar förut…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GIH2NR</t>
+          <t>GIH2LY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - redogöra för rörelseapparatens funktionella anatomi samt biomekani…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GIH2QK</t>
+          <t>GIH2M4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - redogöra för kroppens sensoriska organ samt nervsystemets och musk…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GIH2QL</t>
+          <t>GIH2M5</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1211,24 +1211,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - planera och genomföra träning vars syfte är att utveckla människans a…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GIH2UR</t>
+          <t>GIH2M6</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1238,24 +1238,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för olika vetenskapliga förhållningssätt inom forskning   -…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GIH2UY</t>
+          <t>GIH2NR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1265,24 +1265,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för människans energi- och näringsbehov   - redogöra för och…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GIH2VJ</t>
+          <t>GIH2QK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - visa kunskap om förebyggandet av potentiella idrottsrelaterade skador…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QK</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GIH2VK</t>
+          <t>GIH2QL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1319,24 +1319,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - identifiera, redogöra för och diskutera etiska frågeställningar in…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GIH2WT</t>
+          <t>GIH2UR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1346,24 +1346,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:    - redogöra för fysiologiska förmågors tränings…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GIH2WU</t>
+          <t>GIH2UY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1373,24 +1373,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:    - redogöra för fysiologiska förmågors tränings…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GIH2WX</t>
+          <t>GIH2VJ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1400,24 +1400,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:    - identifiera och redogöra för olika vetenskapliga områden inom idrotts- och…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GIH2WY</t>
+          <t>GIH2VK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1427,24 +1427,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:     - diskutera och problematisera skolämnet idrott och hälsa utifrån olika did…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GIH2X3</t>
+          <t>GIH2WT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1454,24 +1454,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för och diskutera idrottsvetenskap med fokus på träningslära…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GIH2XY</t>
+          <t>GIH2WU</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1481,24 +1481,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs ska studenten:     - ha förmågan att utifrån en datamängd förklara och visualisera en variabels centr…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2XY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WU</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GIH35B</t>
+          <t>GIH2WX</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1508,24 +1508,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en fördjupad nivå kunna:       - sammanställa kunskapsläget, utifrån relevant…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GIH35W</t>
+          <t>GIH2WY</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1535,24 +1535,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs ska den studerande på en fördjupad nivå kunna:    - sammanställa kunskapsläget, utifrån relevant fors…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GIH37N</t>
+          <t>GIH2X3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1562,24 +1562,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GIH37P</t>
+          <t>GIH2ZA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1589,24 +1589,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.   ### Delkurser  1…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZA</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH2ZB</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GIH37R</t>
+          <t>GIH2ZC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande, utifrån den kunskapsbas som lagts i Idrott och hälsa I med didaktisk inr…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GIH37S</t>
+          <t>GIH2ZD</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1670,24 +1670,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper i idrotts- och hälsovetenskap med foku…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GIH392</t>
+          <t>GIH2ZE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1697,24 +1697,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:     - diskutera och problematisera skolämnet idrott och hälsa utifrån olika did…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH392</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZE</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GIH394</t>
+          <t>GIH32Z</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1724,24 +1724,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:    - identifiera och redogöra för olika vetenskapliga områden inom idrotts- och…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH394</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH32Z</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GIH3AM</t>
+          <t>GIH334</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1751,24 +1751,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs ska studenten på en grundläggande nivå kunna:    - reflektera över och diskutera tränarrollen utifrån…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH334</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GIH3AN</t>
+          <t>GIH335</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1778,24 +1778,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.   ### Delkurser  1…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH335</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>GIH33J</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1805,24 +1805,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GIH3D4</t>
+          <t>GIH33K</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1832,24 +1832,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för och diskutera idrottsvetenskap med fokus på träningslära…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GIH3D5</t>
+          <t>GIH33P</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1859,24 +1859,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för och diskutera idrottsvetenskap med fokus på träningslära…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GIH3D6</t>
+          <t>GIH34D</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1886,24 +1886,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för människans energi- och näringsbehov   - redogöra för och…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GIH3GA</t>
+          <t>GIH34S</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1913,24 +1913,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs ska den studerande på en fördjupad nivå kunna:    - utifrån ett valt syfte, designa och genomföra en…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>IH1001</t>
+          <t>GIH34T</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1940,24 +1940,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursen består av fyra delkurser med mål enligt nedanstående.  ### Delkurser  1.Motorik, anatomi och fysiologi I, 7,5 hög…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>IH1002</t>
+          <t>GIH34U</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1967,24 +1967,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursen består av fyra delkurser med mål enligt nedanstående.  ### Delkurser  1.Motorik, anatomi och fysiologi II, 7,5 hö…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34U</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>IH1003</t>
+          <t>GIH34V</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1994,24 +1994,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna    - redogöra för, samt analysera hur olika faktorer påverkar barns och u…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>IH1004</t>
+          <t>GIH35B</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2021,24 +2021,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna    - redogöra för, samt analysera hur livsvillkor och fritidsvanor påverk…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en fördjupad nivå kunna:…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>IH1005</t>
+          <t>GIH35P</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2048,24 +2048,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig kunskaper om rörelse som eget kunskapsområde och som medel…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>IH1006</t>
+          <t>GIH35T</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2075,24 +2075,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - visa kunskaper om rörelse som erfarenhet, upplevelse och aktivitet ur…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35T</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>IH1007</t>
+          <t>GIH35U</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2102,24 +2102,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna:    - reflektera kring och analysera dansen som kunskapsområde,    - till…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35U</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>IH1008</t>
+          <t>GIH35V</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:          - använda och värdera ett brett spektrum av mätmetoder för att an…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>IH1009</t>
+          <t>GIH35W</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2156,24 +2156,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna         - visa goda kunskaper om** **barns och ungdomars motoriska och pe…</t>
+          <t>Avviker från gold standard: Efter godkänd kurs ska den studerande på en fördjupad nivå kunna:…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35W</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>IH1010</t>
+          <t>GIH35Z</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2183,24 +2183,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna         - visa färdigheter i friluftsteknik och friluftssäkerhet i olika…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>IH1011</t>
+          <t>GIH37B</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2210,24 +2210,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna:    - påvisa och argumentera för rörelsens och naturens betydelse för bar…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>IH1012</t>
+          <t>GIH37C</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2237,24 +2237,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna         - redogöra för och analysera utövandet av idrott och friluftsliv i…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>IH1015</t>
+          <t>GIH37N</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2264,24 +2264,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - redogöra för grunderna i socialpsykologiska teorier, vad gäller in…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>IH1020</t>
+          <t>GIH37P</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2291,24 +2291,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig kunskaper om och förståelse för humanbiologiska och socialp…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.   ### Delkurser  1…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>IH1023</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2318,24 +2318,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - använda ett brett spektrum av mätmetoder för att analysera, styr…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>IH1024</t>
+          <t>GIH37R</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2345,24 +2345,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - använda och värdera ett brett spektrum av mätmetoder för evaluer…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande, utifrån den kunskapsbas som lagts i Idrott och hälsa I med didaktisk inr…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>IH1025</t>
+          <t>GIH37S</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2372,24 +2372,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - använda ett brett spektrum av mätmetoder för att analysera, styr…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper i idrotts- och hälsovetenskap med foku…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>IH1026</t>
+          <t>GIH38Y</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2399,24 +2399,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - reflektera över förebyggande, omhändertagande och rehabilitering…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Y</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>IH1029</t>
+          <t>GIH38Z</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2426,24 +2426,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Avvikande introfras: ### Delkurser  1.Idrott och hälsa - ett ämne för alla?, 15 högskolepoäng  Efter avslutad delkurs skall den studerande ku…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Z</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>IH1062</t>
+          <t>GIH392</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2453,24 +2453,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig kunskaper och förståelse för fysiologiska och motivationsps…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH392</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>IH1082</t>
+          <t>GIH393</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2480,24 +2480,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Studenten ska efter genomförd kurs kunna:         - redogöra för idrottsjournalistikens utveckling    - visa förståelse…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1082</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH393</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>IH1095</t>
+          <t>GIH394</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2507,24 +2507,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna         - visa förmåga att använda olika metoder för att utvärdera en affär…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH394</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>IH1096</t>
+          <t>GIH395</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2534,24 +2534,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - upprätta en affärsmodell.…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH395</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>IH1097</t>
+          <t>GIH39B</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - visa hur nätverk och partnerskap kan byggas.…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39B</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>IH1098</t>
+          <t>GIH39C</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2588,24 +2588,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - visa förmåga att identifiera och föreslå lösningar på ett markna…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39C</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>IH1099</t>
+          <t>GIH39D</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2615,24 +2615,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - redogöra för metoder för bedömning av en affärsidés finansiering…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39D</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>IH1100</t>
+          <t>GIH39E</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2642,24 +2642,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - visa förmåga att kritiskt diskutera affärsetiska frågor utifrån…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39E</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>IH1101</t>
+          <t>GIH39F</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2669,24 +2669,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - redogöra för hur en produktutvecklingsprocess kan planeras och k…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39F</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>IH1102</t>
+          <t>GIH39G</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2696,24 +2696,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - visa förmåga att tillämpa en produktutvecklingsmodell som stöd f…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39G</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>IH1111</t>
+          <t>GIH39H</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2723,24 +2723,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Studenten ska efter genomförd kurs kunna:         - redogöra för idrottsjournalistikens utveckling    - visa förståelse…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1111</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39H</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>IH1113</t>
+          <t>GIH3AM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2750,24 +2750,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - tillämpa grundläggande kunskaper inom ämnesområdet fysisk träning med…</t>
+          <t>Avviker från gold standard: Efter godkänd kurs ska studenten på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>IH1114</t>
+          <t>GIH3AN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2777,24 +2777,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för de viktigaste mikro- och makronutrienterna och deras bet…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.   ### Delkurser  1…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>IH1122</t>
+          <t>GIH3AP</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2804,24 +2804,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna       - definiera begreppet sportmedia     - analysera relationen mellan sa…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1122</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>IH1130</t>
+          <t>GIH3AQ</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2831,24 +2831,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - redogöra för kroppens sensoriska organ samt nervsystemets och musk…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>IH2001</t>
+          <t>GIH3C2</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2858,24 +2858,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna    - uppvisa ett kritiskt vetenskapligt förhållningssätt till forskning r…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3C2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>IH2002</t>
+          <t>GIH3CS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2885,24 +2885,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Avvikande introfras: ### Delkurser  1.Träningslära, 7,5 högskolepoäng  Efter avslutad delkurs skall den studerande kunna    - analysera och v…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>IH2003</t>
+          <t>GIH3D4</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2912,24 +2912,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna:         - visa färdigheter i och förtrogenhet med friluftsteknik och fri…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>IH2004</t>
+          <t>GIH3D5</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2939,24 +2939,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna:    - kommunicera och problematisera begreppet och fenomenet hälsa ur oli…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>IH2005</t>
+          <t>GIH3D6</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2966,24 +2966,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna:    - visa färdigheter i rörelse till olika former av musik    - analyser…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>IH2006</t>
+          <t>GIH3F4</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2993,24 +2993,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna    - analysera och värdera olika idrotts- och motionsaktiviteter ur ett h…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>IH3007</t>
+          <t>GIH3F5</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3020,2938 +3020,5638 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - identifiera ett vetenskapsteoretiskt problem samt kunna tillämpa…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>BKE223</t>
+          <t>GIH3F7</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KEA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om kemi.  Efter avslutad kurs…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BKE223</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F7</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>AMC22C</t>
+          <t>GIH3F8</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Den studerande ska efter genomgången kurs självständigt kunna:    - tillämpa och kritiskt reflektera över teorier och mo…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC22C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>AMC243</t>
+          <t>GIH3F9</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - ingående beskriva nociception, smärtmodulering och smärtupplevelse ur…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F9</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>AMC24R</t>
+          <t>GIH3FA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande självständigt kunna:    - redogöra för etiologi, symtom, fysiologi, patofysiologi…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FA</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>AMC25W</t>
+          <t>GIH3FD</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande självständigt kunna:    - tillämpa och värdera ett personcentrerat förhållningssä…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC25W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FD</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>AMC265</t>
+          <t>GIH3FF</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      -  redogöra för farmakokinetik, farmakodynamik, biverkningar och inte…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FF</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>AMC2BG</t>
+          <t>GIH3G4</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs ska den studerande självständigt kunna:    - redogöra för farmakokinetik, farmakodynamik samt identif…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GMC22H</t>
+          <t>GIH3G5</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska ha kunskap om byggnad och funktion hos den friska människokroppen.  E…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GMC2AH</t>
+          <t>GIH3G6</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - förklara humana cellers grundläggande funktioner och hur celler sa…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GMC2M2</t>
+          <t>GIH3G7</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - beskriva människans anatomi och fysiologiska processer avseende: mats…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G7</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>MC1072</t>
+          <t>GIH3G8</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska ha kunskap om byggnad och funktion hos den friska människokroppen.    Efte…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>MC1077</t>
+          <t>GIH3G9</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska ha kunskaper inom klinisk mikrobiologi, allmän farmakologi och läkemedelsh…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>MC1079</t>
+          <t>GIH3GA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska tillägna sig grundläggande kunskaper inom allmän farmakologi, läkemed…</t>
+          <t>Avviker från gold standard: Efter godkänd kurs ska den studerande på en fördjupad nivå kunna:…</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>MC2017</t>
+          <t>GIH3GB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       -  redogöra för grundläggande medicinska begrepp såsom psykisk sjukd…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GB</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>MC2020</t>
+          <t>GIH3GC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på ett professionellt, systematiskt och självständigt sätt och utifrån en helhets…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>MC3027</t>
+          <t>GIH3GD</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande självständigt kunna:         - redogöra för farmakokinetik, farmakodynamik samt i…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GD</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GNV2KY</t>
+          <t>GIH3GE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper i och om naturvetenskap och teknik rele…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GE</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>NV1024</t>
+          <t>GIH3GF</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande syftet med denna kurs är att kursdeltagarna ska utveckla sin didaktiska medvetenhet och praktiska skick…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GF</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>NV1027</t>
+          <t>GIH3GG</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att deltagarna utvecklar kunskap om och förmåga att arbeta med hållbar utveckling.    Efter…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GG</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>NV1035</t>
+          <t>GIH3GH</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om naturorienterande ämnen oc…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GH</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>NV3001</t>
+          <t>GIH3GJ</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att kursdeltagaren ska utveckla kunskaper och förhållningssätt som ökar förutsättningarna fö…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GJ</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>PS1018</t>
+          <t>GIH3GK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PSA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - beskriva grunderna för stödjande samtal    - redogöra för grunderna i…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PS1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GK</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>ASA24J</t>
+          <t>GIH3JL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:    - visa fördjupad kunskap om och kritiskt gransk…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3JL</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>ASA24K</t>
+          <t>IH1001</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna    - redogöra på ett fördjupat sätt för centrala be…</t>
+          <t>Avviker från gold standard: Kursen består av fyra delkurser med mål enligt nedanstående.  ### Delkurser  1.Motorik, anatomi och fysiologi I, 7,5 hög…</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1001</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>ASA24L</t>
+          <t>IH1002</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande under kursen ska tillägna sig fördjupade kunskaper om barn och ungas utve…</t>
+          <t>Avviker från gold standard: Kursen består av fyra delkurser med mål enligt nedanstående.  ### Delkurser  1.Motorik, anatomi och fysiologi II, 7,5 hö…</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>ASA24M</t>
+          <t>IH1003</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik i vård och omsorg utifrån persp…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1003</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>ASA24N</t>
+          <t>IH1004</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska uppnå en bredare och djupare kompetens om äldre personer och åldrande utif…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1004</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>ASA266</t>
+          <t>IH1005</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse   Efter avslutad kurs ska den studerande kunna:    - visa fördjupade kunskaper om samhälleliga li…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig kunskaper om rörelse som eget kunskapsområde och som medel …</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1005</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>ASA26U</t>
+          <t>IH1006</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande självständigt kunna:    - visa fördjupad kunskap om olika…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1006</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>ASA27E</t>
+          <t>IH1007</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Kunskap och förståelse **    Efter avslutad kurs ska den studerande kunna:      - visa fördjupad kunskap om aktuell na…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1007</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>ASA28A</t>
+          <t>IH1008</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik i vård och omsorg utifrån persp…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA28A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1008</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GSA24U</t>
+          <t>IH1009</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:    - redogöra för olika teoretiska perspektiv på v…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1009</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>IH1010</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse  Den studerande ska efter avslutad kurs kunna:    - visa kunskap om och förståelse för samspelet…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1010</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GSA27Y</t>
+          <t>IH1011</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna visa grundläggande kunskaper om:    - psykologi som…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>IH1012</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:    - visa kunskaper om nationell och internationel…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>IH1015</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Avvikande introfras: unskap och förståelse  Efter avslutad kurs ska den studerande kunna:    - visa teoretiska och praktiska kunskaper om arb…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1015</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>IH1020</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig kunskaper om och förståelse för humanbiologiska och socialp…</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1020</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GSA2E3</t>
+          <t>IH1023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna:      - visa fördjupade kunskaper om olika former…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1023</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GSA2E4</t>
+          <t>IH1024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:    - visa kunskap om och förståelse för hur familj…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1024</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GSA2E5</t>
+          <t>IH1025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse        Efter avslutad kurs ska den studerande kunna:    - beskriva olika utredningar och handlägg…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1025</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GSA2GZ</t>
+          <t>IH1026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - redogöra för begrepp, idéer, arbetssätt och teoretiska grunder i k…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1026</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GSA2NA</t>
+          <t>IH1029</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:    - på grundläggande nivå redogöra för olika vete…</t>
+          <t>Avviker från gold standard: ### Delkurser  1.Idrott och hälsa - ett ämne för alla?, 15 högskolepoäng  Efter avslutad delkurs skall den studerande ku…</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GSA2NC</t>
+          <t>IH1062</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Moment 1. Campusförlagd utbildning, 5 högskolepoäng**  Kunskap och förståelse    Efter avslutat moment ska den studera…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig kunskaper och förståelse för fysiologiska och motivationsps…</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GSA2RE</t>
+          <t>IH1082</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Kunskap och förståelse**    Efter avslutad kurs ska den studerande kunna:      - redogöra för olika socialpolitiska mo…</t>
+          <t>Avviker från gold standard: Studenten ska efter genomförd kurs kunna:…</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1082</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GSA2SD</t>
+          <t>IH1095</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Kunskap och förståelse**   Efter avslutad kurs ska den studerande kunna:       - visa kunskap om och förståelse för hu…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GSA2SE</t>
+          <t>IH1096</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Kunskap och förståelse   **Efter avslutad kurs ska den studerande kunna:    - visa fördjupade och vidgade kunskaper om…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GSA32Y</t>
+          <t>IH1097</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunna:…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>IH1098</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GSA3DS</t>
+          <t>IH1099</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunna:…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GSA3FL</t>
+          <t>IH1100</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Modul 1. Campusförlagd utbildning, 4,5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunn…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>SA1032</t>
+          <t>IH1101</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för socialarbetarprogrammets idé om verksamhetsförlagd utbil…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>SA1037</t>
+          <t>IH1102</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripandemål är att studenten inhämtat kunskap om teoretisk grund och evidensbas för återfallsprevention samt…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>SA1040</t>
+          <t>IH1111</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska tillägna sig kunskaper inom Motiverande samtal (MI) med inriktning på…</t>
+          <t>Avviker från gold standard: Studenten ska efter genomförd kurs kunna:…</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1111</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>SA1045</t>
+          <t>IH1113</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna:       - på en grundläggande nivå redogöra för ol…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>SA1046</t>
+          <t>IH1114</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - beskriva konsekvenser av mäns våld mot kvinnor och barn på individ-…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>IH1122</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1122</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>IH1130</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att studenten skall ha fördjupat sina kunskaper om vetenskaplig metod, evidens och utvärderi…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>SA3008</t>
+          <t>IH2001</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_  Efter avslutad kurs ska den studerande kunna:    - visa fördjupade kunskaper om nationell och…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>ASR22N</t>
+          <t>IH2002</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska kunna identifiera barnmorskelärarens roll i att planera och genomföra…</t>
+          <t>Avviker från gold standard: ### Delkurser  1.Träningslära, 7,5 högskolepoäng  Efter avslutad delkurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>ASR24V</t>
+          <t>IH2003</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för centrala begrepp inom global sexuell och reproduktiv häl…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2003</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>ASR24W</t>
+          <t>IH2004</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - självständigt och systematiskt söka efter relevanta vetenskapliga art…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2004</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>ASR24X</t>
+          <t>IH2005</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - visa kunskap om evidensbaserade metoder för implementering av kvalite…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>ASR25P</t>
+          <t>IH2006</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid okomplicerad graviditet, förlossning…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2006</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>ASR25Q</t>
+          <t>IH3007</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid komplicerad graviditet, förlossning…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH3007</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>ASR25T</t>
+          <t>BKE223</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>KEA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - applicera och anpassa evidensbaserad kunskap om global sexuell och re…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om kemi.  Efter avslutad kurs…</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BKE223</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>ASR25U</t>
+          <t>AMC22C</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - problematisera principer som ligger till grund för rättssäkerhet och…</t>
+          <t>Avviker från gold standard: Den studerande ska efter genomgången kurs självständigt kunna:…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC22C</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>ASR25V</t>
+          <t>AMC243</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande självständigt kunna:    - genomföra en vetenskaplig undersökning med relevant des…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>ASR26N</t>
+          <t>AMC24R</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - säkerställa progressionen från utbildningsplan och kursplaner på kand…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>ASR26S</t>
+          <t>AMC25W</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid komplicerad graviditet, förlossning…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC25W</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>ASR284</t>
+          <t>AMC265</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>ASR286</t>
+          <t>AMC28N</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC28N</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>ASR296</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR296</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>ASR29S</t>
+          <t>AMC29Y</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs ska studenten självständigt kunna    - kritiskt reflektera över och analysera begrepp, teorier och pe…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>ASR29U</t>
+          <t>AMC2A7</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs ska studenten självständigt kunna:    - i simulerad miljö utföra undersökningar och behandlingar vid…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>AMC2BG</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs ska studenten på en fördjupad nivå kunna:    - kritiskt reflektera över begrepp, teorier och hållbarh…</t>
+          <t>Avviker från gold standard: Efter godkänd kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>ASR2CH</t>
+          <t>GMC22H</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs ska studenten självständigt kunna:    - genomföra en vetenskaplig undersökning med relevant design, m…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska ha kunskap om byggnad och funktion hos den friska människokroppen.  E…</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GSR2A5</t>
+          <t>GMC2AH</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna    - redovisa kunskaper för ungdomar och unga vuxnas reproduktiva hälsa i e…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2AH</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GSR2KZ</t>
+          <t>GMC2M2</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - beskriva hälsa, jämlikhet och jämställdhet utifrån hållbarhetsmålen 2…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>SR3001</t>
+          <t>GMC32X</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska fördjupa och integrera kunskaper om barnmorskans arbetsfält och ansva…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC32X</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>SR3002</t>
+          <t>GMC37E</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om kvalitativa och kvantitativa metoder, utve…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>SR3003</t>
+          <t>GMC37F</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska utveckla fördjupad förståelse för global sexuell och reproduktiv häls…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37F</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>SR3004</t>
+          <t>GMC37T</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska kunna utveckla och tillämpa ett i praktiken hållbart vetenskapligt fö…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37T</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>SR3005</t>
+          <t>MC1072</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska visa fördjupade kunskaper om barnmorskans arbetsfält och ansvarsområd…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att studenten ska ha kunskap om byggnad och funktion hos den friska människokroppen.    Efte…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>SR3006</t>
+          <t>MC1077</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska visa fördjupade metodkunskaper och fördjupad förmåga att integrera ku…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att studenten ska ha kunskaper inom klinisk mikrobiologi, allmän farmakologi och läkemedelsh…</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>SR3007</t>
+          <t>MC1079</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska kunna visa fördjupade metodkunskaper och förmåga att integrera kunska…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska tillägna sig grundläggande kunskaper inom allmän farmakologi, läkemed…</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>SR3008</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska tillägna sig kunskaper om barnmorskans arbetsfält och ansvarsområde.…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>MC3027</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om sexuell och reproduktiv hälsa som en mänsk…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>SR3010</t>
+          <t>GNV2KY</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripade mål är att den studerande ska förstå förlopp och processer vid normal och komplicerad graviditet, fö…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper i och om naturvetenskap och teknik rele…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>SR3011</t>
+          <t>GNV396</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>GNV3GU</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GU</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>SR3013</t>
+          <t>GNV3GV</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>SR3014</t>
+          <t>NV1024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursen övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt kan tillämpa, ytt…</t>
+          <t>Avviker från gold standard: Det övergripande syftet med denna kurs är att kursdeltagarna ska utveckla sin didaktiska medvetenhet och praktiska skick…</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1024</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>NV1027</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt ska fördjupa och…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att deltagarna utvecklar kunskap om och förmåga att arbeta med hållbar utveckling.    Efter …</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1027</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>AVV26K</t>
+          <t>NV1035</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för historisk utveckling, teoretiska modeller och centrala b…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om naturorienterande ämnen oc…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>AVV26M</t>
+          <t>NV3001</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande, med tillämpning inom hälso- och sjukvård och socialt arb…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att kursdeltagaren ska utveckla kunskaper och förhållningssätt som ökar förutsättningarna fö…</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>VV2001</t>
+          <t>PS1018</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>PSA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att studenten tillägnar sig kunskaper om handledning och handledningssituationer som är spec…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PS1018</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>VV2002</t>
+          <t>ASA24J</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna    - redogöra för gällande regelverk för olika professioner inom kommunal äldreo…</t>
+          <t>Avviker från gold standard: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>VV3003</t>
+          <t>ASA24K</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - analysera och bedöma relevansen i problemformuleringar inom vårdveten…</t>
+          <t>Avviker från gold standard: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>VV3006</t>
+          <t>ASA24L</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Kunskap och förståelse**   Efter avslutad kurs ska studenten kunna         - diskutera och reflektera över barnmorskep…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande under kursen ska tillägna sig fördjupade kunskaper om barn och ungas utve…</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>VV3007</t>
+          <t>ASA24M</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Kunskap och förståelse**   Efter avslutad kurs ska studenten kunna    - redogöra för och diskutera begreppen normal gr…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik i vård och omsorg utifrån persp…</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>VV3009</t>
+          <t>ASA24N</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Kunskap och förståelse   **Efter avslutad kurs ska studenten kunna:    - kommunicera, diskutera och försvara vetenskap…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att studenten ska uppnå en bredare och djupare kompetens om äldre personer och åldrande utif…</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>VV3010</t>
+          <t>ASA266</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
+          <t>Avviker från gold standard: Kunskap och förståelse   Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>VV3011</t>
+          <t>ASA26U</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
+          <t>Avviker från gold standard: Kunskap och förståelse  Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>VV3012</t>
+          <t>ASA27E</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap…</t>
+          <t>Avviker från gold standard: **Kunskap och förståelse **    Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>VV3014</t>
+          <t>ASA28A</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik i vård och omsorg utifrån persp…</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA28A</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>VV3015</t>
+          <t>ASA28Q</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA28Q</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
+          <t>ASA293</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA293</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>ASA2BA</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA2BA</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>GSA24U</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>GSA24V</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kunskap och förståelse  Den studerande ska efter avslutad kurs kunna:…</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>GSA27Y</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna visa grundläggande kunskaper om:…</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>GSA2AF</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>GSA2BV</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: unskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>GSA2DW</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>GSA2E3</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>GSA2E4</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>GSA2E5</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kunskap och förståelse        Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>GSA2GZ</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>GSA2NA</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>GSA2NC</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: **Moment 1. Campusförlagd utbildning, 5 högskolepoäng**  Kunskap och förståelse    Efter avslutat moment ska den studera…</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>GSA2RE</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: **Kunskap och förståelse**    Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>GSA2SD</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: **Kunskap och förståelse**   Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>GSA2SE</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: **Kunskap och förståelse   **Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>GSA32Y</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>GSA352</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA352</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>GSA3AS</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DM</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DN</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DP</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DP</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DQ</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DR</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DR</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DS</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>GSA3FK</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>GSA3FL</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: **Modul 1. Campusförlagd utbildning, 4,5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunn…</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>GSA3HA</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>SA1032</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>SA1037</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripandemål är att studenten inhämtat kunskap om teoretisk grund och evidensbas för återfallsprevention samt…</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>SA1040</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska tillägna sig kunskaper inom Motiverande samtal (MI) med inriktning på…</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>SA1045</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>SA1046</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>SA1048</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>SA2020</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att studenten skall ha fördjupat sina kunskaper om vetenskaplig metod, evidens och utvärderi…</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>SA3008</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: _Kunskap och förståelse_  Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>ASR22N</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska kunna identifiera barnmorskelärarens roll i att planera och genomföra…</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>ASR24V</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>ASR24W</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>ASR24X</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>ASR25P</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid okomplicerad graviditet, förlossning…</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>ASR25Q</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid komplicerad graviditet, förlossning …</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>ASR25T</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25T</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>ASR25U</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>ASR25V</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande självständigt kunna:…</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>ASR26N</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>ASR26S</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid komplicerad graviditet, förlossning …</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>ASR284</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>ASR285</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>ASR286</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>ASR296</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR296</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>ASR29S</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter godkänd kurs ska studenten självständigt kunna…</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>ASR29T</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>ASR29U</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter godkänd kurs ska studenten självständigt kunna:…</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>ASR29V</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter godkänd kurs ska studenten på en fördjupad nivå kunna:…</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>ASR29W</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>ASR2AD</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>ASR2B9</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>ASR2BM</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2BM</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>ASR2CE</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>ASR2CF</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CF</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>ASR2CG</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CG</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>ASR2CH</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter godkänd kurs ska studenten självständigt kunna:…</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CH</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>ASR2CJ</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>ASR2CK</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CK</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>GSR2A5</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna…</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>GSR2KZ</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>GSR2ZH</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2ZH</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>GSR38B</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>GSR3BZ</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR3BZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>SR3001</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska fördjupa och integrera kunskaper om barnmorskans arbetsfält och ansva…</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>SR3002</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om kvalitativa och kvantitativa metoder, utve…</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>SR3003</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska utveckla fördjupad förståelse för global sexuell och reproduktiv häls…</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>SR3004</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska kunna utveckla och tillämpa ett i praktiken hållbart vetenskapligt fö…</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>SR3005</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska visa fördjupade kunskaper om barnmorskans arbetsfält och ansvarsområd…</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>SR3006</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska visa fördjupade metodkunskaper och fördjupad förmåga att integrera ku…</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>SR3007</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska kunna visa fördjupade metodkunskaper och förmåga att integrera kunska…</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>SR3008</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska tillägna sig kunskaper om barnmorskans arbetsfält och ansvarsområde. …</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>SR3009</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om sexuell och reproduktiv hälsa som en mänsk…</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>SR3010</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripade mål är att den studerande ska förstå förlopp och processer vid normal och komplicerad graviditet, fö…</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>SR3011</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>SR3012</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>SR3013</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>SR3014</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursen övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt kan tillämpa, ytt…</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>SR3015</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt ska fördjupa och…</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>AVV26K</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>AVV2A6</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>GVV3JJ</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVV3JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>GVV3JK</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVV3JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>VV2001</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att studenten tillägnar sig kunskaper om handledning och handledningssituationer som är spec…</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>VV2002</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna…</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>VV3003</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>VV3006</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: **Kunskap och förståelse**   Efter avslutad kurs ska studenten kunna…</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>VV3007</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: **Kunskap och förståelse**   Efter avslutad kurs ska studenten kunna…</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>VV3009</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: **Kunskap och förståelse   **Efter avslutad kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>VV3010</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>VV3012</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap …</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>VV3014</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>VV3015</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
           <t>VV3017</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B304" t="inlineStr">
         <is>
           <t>VÅE</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Avvikande formulering</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>Avvikande introfras: Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap,…</t>
-        </is>
-      </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap,…</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E204"/>
+  <autoFilter ref="A1:E304"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -6359,6 +9059,206 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A208" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A211" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A212" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A213" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A214" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A215" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A216" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A217" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A218" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A219" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A221" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A222" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A223" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A224" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A226" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A227" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A228" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A229" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A230" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A231" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A232" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A233" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A234" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A235" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A236" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A237" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A238" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A239" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A240" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A241" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A242" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A243" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A244" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A245" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A246" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A247" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A248" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A249" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A250" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A251" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A252" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A253" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A254" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A255" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E255" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A256" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A257" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A258" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E258" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A259" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A260" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A261" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A262" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A263" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E263" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A264" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A265" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A266" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A267" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A268" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A269" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E269" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A270" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E270" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A271" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A272" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A273" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A274" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A275" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A276" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E276" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A277" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E277" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A278" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E278" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A279" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E279" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A280" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A281" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A282" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A283" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A284" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A285" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A286" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A287" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A288" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A289" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A290" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E290" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A291" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E291" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A292" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E292" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A293" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A294" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A295" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A296" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A297" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A298" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A299" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A300" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A301" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E301" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A302" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E302" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A303" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A304" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId606"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$304</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$200</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E304"/>
+  <dimension ref="A1:E200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,115 +472,115 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AFT2C8</t>
+          <t>AIH237</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FYS</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AFT2C9</t>
+          <t>AIH24T</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FYS</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AFT2CA</t>
+          <t>GIH24A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FYS</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2CA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH24A</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AFT2CB</t>
+          <t>GIH2A6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FYS</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2A6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AIH237</t>
+          <t>GIH2D4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -590,24 +590,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AIH24T</t>
+          <t>GIH2D5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -617,24 +617,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GIH24A</t>
+          <t>GIH2D6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -644,24 +644,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna redogöra för:…</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH24A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GIH2A6</t>
+          <t>GIH2D7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna redogöra för:…</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GIH2D4</t>
+          <t>GIH2D8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -698,24 +698,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GIH2D5</t>
+          <t>GIH2D9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -725,24 +725,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GIH2D6</t>
+          <t>GIH2DB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -752,24 +752,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna redogöra för:…</t>
+          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DB</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GIH2D7</t>
+          <t>GIH2DC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -779,24 +779,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna redogöra för:…</t>
+          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GIH2D8</t>
+          <t>GIH2DD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -806,24 +806,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GIH2D9</t>
+          <t>GIH2DE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -833,24 +833,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GIH2DB</t>
+          <t>GIH2G4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -860,24 +860,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GIH2DC</t>
+          <t>GIH2LP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -887,24 +887,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LP</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GIH2DD</t>
+          <t>GIH2LT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -914,24 +914,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GIH2DE</t>
+          <t>GIH2LU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -941,24 +941,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GIH2G4</t>
+          <t>GIH2LV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -968,24 +968,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GIH2LP</t>
+          <t>GIH2LW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -995,24 +995,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GIH2LT</t>
+          <t>GIH2LX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1022,24 +1022,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GIH2LU</t>
+          <t>GIH2LY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1049,24 +1049,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GIH2LV</t>
+          <t>GIH2M4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GIH2LW</t>
+          <t>GIH2M5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1103,24 +1103,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GIH2LX</t>
+          <t>GIH2M6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GIH2LY</t>
+          <t>GIH2NR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GIH2M4</t>
+          <t>GIH2QK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QK</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GIH2M5</t>
+          <t>GIH2QL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1211,24 +1211,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GIH2M6</t>
+          <t>GIH2UR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1238,24 +1238,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GIH2NR</t>
+          <t>GIH2UY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1265,24 +1265,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GIH2QK</t>
+          <t>GIH2VJ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GIH2QL</t>
+          <t>GIH2VK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1319,24 +1319,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GIH2UR</t>
+          <t>GIH2WT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1346,24 +1346,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GIH2UY</t>
+          <t>GIH2WU</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1373,24 +1373,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WU</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GIH2VJ</t>
+          <t>GIH2WX</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1400,24 +1400,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GIH2VK</t>
+          <t>GIH2WY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1427,24 +1427,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GIH2WT</t>
+          <t>GIH2X3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1454,24 +1454,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GIH2WU</t>
+          <t>GIH35B</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1481,24 +1481,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande på en fördjupad nivå kunna:…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GIH2WX</t>
+          <t>GIH35W</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1508,24 +1508,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande på en fördjupad nivå kunna:…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35W</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GIH2WY</t>
+          <t>GIH37N</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1535,24 +1535,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GIH2X3</t>
+          <t>GIH37P</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1562,24 +1562,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.   ### Delkurser  1…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZA</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1589,24 +1589,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZB</t>
+          <t>GIH37R</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande, utifrån den kunskapsbas som lagts i Idrott och hälsa I med didaktisk inr…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZC</t>
+          <t>GIH37S</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper i idrotts- och hälsovetenskap med foku…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZD</t>
+          <t>GIH392</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1670,24 +1670,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH392</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZE</t>
+          <t>GIH394</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1697,24 +1697,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH394</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GIH32Z</t>
+          <t>GIH3AM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1724,24 +1724,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter godkänd kurs ska studenten på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH32Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GIH334</t>
+          <t>GIH3AN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1751,24 +1751,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.   ### Delkurser  1…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH334</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GIH335</t>
+          <t>GIH3AP</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1778,24 +1778,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH335</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GIH33J</t>
+          <t>GIH3D4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1805,24 +1805,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GIH33K</t>
+          <t>GIH3D5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1832,24 +1832,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GIH33P</t>
+          <t>GIH3D6</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1859,24 +1859,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GIH34D</t>
+          <t>GIH3GA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1886,24 +1886,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter godkänd kurs ska den studerande på en fördjupad nivå kunna:…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GIH34S</t>
+          <t>IH1001</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1913,24 +1913,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursen består av fyra delkurser med mål enligt nedanstående.  ### Delkurser  1.Motorik, anatomi och fysiologi I, 7,5 hög…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1001</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GIH34T</t>
+          <t>IH1002</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1940,24 +1940,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursen består av fyra delkurser med mål enligt nedanstående.  ### Delkurser  1.Motorik, anatomi och fysiologi II, 7,5 hö…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GIH34U</t>
+          <t>IH1003</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1967,24 +1967,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1003</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GIH34V</t>
+          <t>IH1004</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1994,24 +1994,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1004</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GIH35B</t>
+          <t>IH1005</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2021,24 +2021,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande på en fördjupad nivå kunna:…</t>
+          <t>Kursens övergripande mål är att den studerande tillägnar sig kunskaper om rörelse som eget kunskapsområde och som medel …</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1005</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GIH35P</t>
+          <t>IH1006</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2048,24 +2048,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1006</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GIH35T</t>
+          <t>IH1007</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2075,24 +2075,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1007</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GIH35U</t>
+          <t>IH1008</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2102,24 +2102,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1008</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GIH35V</t>
+          <t>IH1009</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1009</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GIH35W</t>
+          <t>IH1010</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2156,24 +2156,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter godkänd kurs ska den studerande på en fördjupad nivå kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1010</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GIH35Z</t>
+          <t>IH1011</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2183,24 +2183,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GIH37B</t>
+          <t>IH1012</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2210,24 +2210,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GIH37C</t>
+          <t>IH1015</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2237,24 +2237,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1015</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GIH37N</t>
+          <t>IH1020</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2264,24 +2264,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
+          <t>Kursens övergripande mål är att den studerande tillägnar sig kunskaper om och förståelse för humanbiologiska och socialp…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1020</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GIH37P</t>
+          <t>IH1023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2291,24 +2291,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.   ### Delkurser  1…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1023</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>IH1024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2318,24 +2318,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1024</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GIH37R</t>
+          <t>IH1025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2345,24 +2345,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande, utifrån den kunskapsbas som lagts i Idrott och hälsa I med didaktisk inr…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1025</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GIH37S</t>
+          <t>IH1026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2372,24 +2372,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper i idrotts- och hälsovetenskap med foku…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GIH38Y</t>
+          <t>IH1029</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2399,24 +2399,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>### Delkurser  1.Idrott och hälsa - ett ämne för alla?, 15 högskolepoäng  Efter avslutad delkurs skall den studerande ku…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GIH38Z</t>
+          <t>IH1062</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2426,24 +2426,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande tillägnar sig kunskaper och förståelse för fysiologiska och motivationsps…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GIH392</t>
+          <t>IH1082</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2453,24 +2453,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Studenten ska efter genomförd kurs kunna:…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH392</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1082</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GIH393</t>
+          <t>IH1095</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2480,24 +2480,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH393</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GIH394</t>
+          <t>IH1096</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2507,24 +2507,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH394</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GIH395</t>
+          <t>IH1097</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2534,24 +2534,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH395</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GIH39B</t>
+          <t>IH1098</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GIH39C</t>
+          <t>IH1099</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2588,24 +2588,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GIH39D</t>
+          <t>IH1100</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2615,24 +2615,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GIH39E</t>
+          <t>IH1101</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2642,24 +2642,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GIH39F</t>
+          <t>IH1102</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2669,24 +2669,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GIH39G</t>
+          <t>IH1111</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2696,24 +2696,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Studenten ska efter genomförd kurs kunna:…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1111</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GIH39H</t>
+          <t>IH1113</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2723,24 +2723,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GIH3AM</t>
+          <t>IH1114</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2750,24 +2750,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter godkänd kurs ska studenten på en grundläggande nivå kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GIH3AN</t>
+          <t>IH1122</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2777,24 +2777,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.   ### Delkurser  1…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1122</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>IH1130</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2804,24 +2804,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GIH3AQ</t>
+          <t>IH2001</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2831,24 +2831,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GIH3C2</t>
+          <t>IH2002</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2858,24 +2858,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>### Delkurser  1.Träningslära, 7,5 högskolepoäng  Efter avslutad delkurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3C2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GIH3CS</t>
+          <t>IH2003</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2885,24 +2885,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2003</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GIH3D4</t>
+          <t>IH2004</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2912,24 +2912,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2004</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GIH3D5</t>
+          <t>IH2005</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2939,24 +2939,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GIH3D6</t>
+          <t>IH2006</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2966,24 +2966,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2006</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GIH3F4</t>
+          <t>IH3007</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2993,5665 +2993,2857 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH3007</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GIH3F5</t>
+          <t>BKE223</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>KEA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om kemi.  Efter avslutad kurs…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BKE223</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GIH3F7</t>
+          <t>AMC22C</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Den studerande ska efter genomgången kurs självständigt kunna:…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC22C</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GIH3F8</t>
+          <t>AMC243</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GIH3F9</t>
+          <t>AMC24R</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GIH3FA</t>
+          <t>AMC25W</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC25W</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GIH3FD</t>
+          <t>AMC265</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GIH3FF</t>
+          <t>AMC2BG</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter godkänd kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GIH3G4</t>
+          <t>GMC22H</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande ska ha kunskap om byggnad och funktion hos den friska människokroppen.  E…</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GIH3G5</t>
+          <t>GMC2AH</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2AH</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GIH3G6</t>
+          <t>GMC2M2</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GIH3G7</t>
+          <t>MC1072</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att studenten ska ha kunskap om byggnad och funktion hos den friska människokroppen.    Efte…</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GIH3G8</t>
+          <t>MC1077</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att studenten ska ha kunskaper inom klinisk mikrobiologi, allmän farmakologi och läkemedelsh…</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GIH3G9</t>
+          <t>MC1079</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande ska tillägna sig grundläggande kunskaper inom allmän farmakologi, läkemed…</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GIH3GA</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter godkänd kurs ska den studerande på en fördjupad nivå kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GIH3GB</t>
+          <t>MC3027</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GIH3GC</t>
+          <t>GNV2KY</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper i och om naturvetenskap och teknik rele…</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GIH3GD</t>
+          <t>NV1024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Det övergripande syftet med denna kurs är att kursdeltagarna ska utveckla sin didaktiska medvetenhet och praktiska skick…</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1024</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GIH3GE</t>
+          <t>NV1027</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att deltagarna utvecklar kunskap om och förmåga att arbeta med hållbar utveckling.    Efter …</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1027</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GIH3GF</t>
+          <t>NV1035</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om naturorienterande ämnen oc…</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GIH3GG</t>
+          <t>NV3001</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att kursdeltagaren ska utveckla kunskaper och förhållningssätt som ökar förutsättningarna fö…</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GIH3GH</t>
+          <t>PS1018</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>PSA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PS1018</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GIH3GJ</t>
+          <t>ASA24J</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GIH3GK</t>
+          <t>ASA24K</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GIH3JL</t>
+          <t>ASA24L</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande under kursen ska tillägna sig fördjupade kunskaper om barn och ungas utve…</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3JL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>IH1001</t>
+          <t>ASA24M</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursen består av fyra delkurser med mål enligt nedanstående.  ### Delkurser  1.Motorik, anatomi och fysiologi I, 7,5 hög…</t>
+          <t>Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik i vård och omsorg utifrån persp…</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>IH1002</t>
+          <t>ASA24N</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursen består av fyra delkurser med mål enligt nedanstående.  ### Delkurser  1.Motorik, anatomi och fysiologi II, 7,5 hö…</t>
+          <t>Kursens övergripande mål är att studenten ska uppnå en bredare och djupare kompetens om äldre personer och åldrande utif…</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>IH1003</t>
+          <t>ASA266</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna…</t>
+          <t>Kunskap och förståelse   Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>IH1004</t>
+          <t>ASA26U</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna…</t>
+          <t>Kunskap och förståelse  Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>IH1005</t>
+          <t>ASA27E</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig kunskaper om rörelse som eget kunskapsområde och som medel …</t>
+          <t>**Kunskap och förståelse **    Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>IH1006</t>
+          <t>ASA28A</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik i vård och omsorg utifrån persp…</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA28A</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>IH1007</t>
+          <t>GSA24U</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>IH1008</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Kunskap och förståelse  Den studerande ska efter avslutad kurs kunna:…</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>IH1009</t>
+          <t>GSA27Y</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna…</t>
+          <t>Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna visa grundläggande kunskaper om:…</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>IH1010</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna…</t>
+          <t>Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>IH1011</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>unskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>IH1012</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>IH1015</t>
+          <t>GSA2E3</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>IH1020</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig kunskaper om och förståelse för humanbiologiska och socialp…</t>
+          <t>Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>IH1023</t>
+          <t>GSA2E5</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Kunskap och förståelse        Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>IH1024</t>
+          <t>GSA2GZ</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>IH1025</t>
+          <t>GSA2NA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>IH1026</t>
+          <t>GSA2NC</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>**Moment 1. Campusförlagd utbildning, 5 högskolepoäng**  Kunskap och förståelse    Efter avslutat moment ska den studera…</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>IH1029</t>
+          <t>GSA2RE</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: ### Delkurser  1.Idrott och hälsa - ett ämne för alla?, 15 högskolepoäng  Efter avslutad delkurs skall den studerande ku…</t>
+          <t>**Kunskap och förståelse**    Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>IH1062</t>
+          <t>GSA2SD</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig kunskaper och förståelse för fysiologiska och motivationsps…</t>
+          <t>**Kunskap och förståelse**   Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>IH1082</t>
+          <t>GSA2SE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Studenten ska efter genomförd kurs kunna:…</t>
+          <t>**Kunskap och förståelse   **Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1082</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>IH1095</t>
+          <t>GSA32Y</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna…</t>
+          <t>**Modul 1. Campusförlagd utbildning, 5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>IH1096</t>
+          <t>GSA3DM</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>IH1097</t>
+          <t>GSA3DS</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>**Modul 1. Campusförlagd utbildning, 5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>IH1098</t>
+          <t>GSA3FL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>**Modul 1. Campusförlagd utbildning, 4,5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunn…</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>IH1099</t>
+          <t>SA1032</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1032</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>IH1100</t>
+          <t>SA1037</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Kursens övergripandemål är att studenten inhämtat kunskap om teoretisk grund och evidensbas för återfallsprevention samt…</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>IH1101</t>
+          <t>SA1040</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Kursens övergripande mål är att den studerande ska tillägna sig kunskaper inom Motiverande samtal (MI) med inriktning på…</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>IH1102</t>
+          <t>SA1045</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>IH1111</t>
+          <t>SA1046</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Studenten ska efter genomförd kurs kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1111</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>IH1113</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>IH1114</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Kursens övergripande mål är att studenten skall ha fördjupat sina kunskaper om vetenskaplig metod, evidens och utvärderi…</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>IH1122</t>
+          <t>SA3008</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna…</t>
+          <t>_Kunskap och förståelse_  Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1122</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>IH1130</t>
+          <t>ASR22N</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Kursens övergripande mål är att den studerande ska kunna identifiera barnmorskelärarens roll i att planera och genomföra…</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>IH2001</t>
+          <t>ASR24V</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>IH2002</t>
+          <t>ASR24W</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: ### Delkurser  1.Träningslära, 7,5 högskolepoäng  Efter avslutad delkurs skall den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>IH2003</t>
+          <t>ASR24X</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>IH2004</t>
+          <t>ASR25P</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid okomplicerad graviditet, förlossning…</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>IH2005</t>
+          <t>ASR25Q</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid komplicerad graviditet, förlossning …</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>IH2006</t>
+          <t>ASR25T</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25T</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>IH3007</t>
+          <t>ASR25U</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>BKE223</t>
+          <t>ASR25V</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>KEA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om kemi.  Efter avslutad kurs…</t>
+          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BKE223</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>AMC22C</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Den studerande ska efter genomgången kurs självständigt kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC22C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>AMC243</t>
+          <t>ASR26S</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid komplicerad graviditet, förlossning …</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>AMC24R</t>
+          <t>ASR284</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande självständigt kunna:…</t>
+          <t>Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>AMC25W</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande självständigt kunna:…</t>
+          <t>Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC25W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>AMC265</t>
+          <t>ASR286</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>ASR296</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR296</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>AMC28N</t>
+          <t>ASR29S</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter godkänd kurs ska studenten självständigt kunna…</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC28N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter godkänd kurs ska studenten självständigt kunna:…</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>AMC29Y</t>
+          <t>ASR29V</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter godkänd kurs ska studenten på en fördjupad nivå kunna:…</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>AMC2A7</t>
+          <t>ASR2CH</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter godkänd kurs ska studenten självständigt kunna:…</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CH</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>AMC2BG</t>
+          <t>GSR2A5</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter godkänd kurs ska den studerande självständigt kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GMC22H</t>
+          <t>GSR2KZ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska ha kunskap om byggnad och funktion hos den friska människokroppen.  E…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GMC2AH</t>
+          <t>SR3001</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Kursens övergripande mål är att den studerande ska fördjupa och integrera kunskaper om barnmorskans arbetsfält och ansva…</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GMC2M2</t>
+          <t>SR3002</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om kvalitativa och kvantitativa metoder, utve…</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GMC32X</t>
+          <t>SR3003</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande ska utveckla fördjupad förståelse för global sexuell och reproduktiv häls…</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC32X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GMC37E</t>
+          <t>SR3004</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande ska kunna utveckla och tillämpa ett i praktiken hållbart vetenskapligt fö…</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GMC37F</t>
+          <t>SR3005</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande ska visa fördjupade kunskaper om barnmorskans arbetsfält och ansvarsområd…</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GMC37T</t>
+          <t>SR3006</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande ska visa fördjupade metodkunskaper och fördjupad förmåga att integrera ku…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>MC1072</t>
+          <t>SR3007</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att studenten ska ha kunskap om byggnad och funktion hos den friska människokroppen.    Efte…</t>
+          <t>Kursens övergripande mål är att den studerande ska kunna visa fördjupade metodkunskaper och förmåga att integrera kunska…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>MC1077</t>
+          <t>SR3008</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att studenten ska ha kunskaper inom klinisk mikrobiologi, allmän farmakologi och läkemedelsh…</t>
+          <t>Kursens övergripande mål är att den studerande ska tillägna sig kunskaper om barnmorskans arbetsfält och ansvarsområde. …</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>MC1079</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska tillägna sig grundläggande kunskaper inom allmän farmakologi, läkemed…</t>
+          <t>Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om sexuell och reproduktiv hälsa som en mänsk…</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>MC2017</t>
+          <t>SR3010</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Kursens övergripade mål är att den studerande ska förstå förlopp och processer vid normal och komplicerad graviditet, fö…</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>MC3027</t>
+          <t>SR3011</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande självständigt kunna:…</t>
+          <t>Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GNV2KY</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper i och om naturvetenskap och teknik rele…</t>
+          <t>Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>GNV396</t>
+          <t>SR3013</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GNV3GU</t>
+          <t>SR3014</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursen övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt kan tillämpa, ytt…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt ska fördjupa och…</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>NV1024</t>
+          <t>AVV26K</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande syftet med denna kurs är att kursdeltagarna ska utveckla sin didaktiska medvetenhet och praktiska skick…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>NV1027</t>
+          <t>VV2001</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att deltagarna utvecklar kunskap om och förmåga att arbeta med hållbar utveckling.    Efter …</t>
+          <t>Kursens övergripande mål är att studenten tillägnar sig kunskaper om handledning och handledningssituationer som är spec…</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>NV1035</t>
+          <t>VV2002</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om naturorienterande ämnen oc…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>NV3001</t>
+          <t>VV3003</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att kursdeltagaren ska utveckla kunskaper och förhållningssätt som ökar förutsättningarna fö…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3003</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>PS1018</t>
+          <t>VV3006</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PSA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>**Kunskap och förståelse**   Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PS1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>ASA24J</t>
+          <t>VV3007</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>**Kunskap och förståelse**   Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3007</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>ASA24K</t>
+          <t>VV3009</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna…</t>
+          <t>**Kunskap och förståelse   **Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3009</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>ASA24L</t>
+          <t>VV3010</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande under kursen ska tillägna sig fördjupade kunskaper om barn och ungas utve…</t>
+          <t>Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3010</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>ASA24M</t>
+          <t>VV3012</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik i vård och omsorg utifrån persp…</t>
+          <t>Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap …</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>ASA24N</t>
+          <t>VV3014</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att studenten ska uppnå en bredare och djupare kompetens om äldre personer och åldrande utif…</t>
+          <t>Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>ASA266</t>
+          <t>VV3015</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kunskap och förståelse   Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>ASA26U</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kunskap och förståelse  Efter avslutad kurs ska den studerande självständigt kunna:…</t>
+          <t>Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap,…</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>ASA27E</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: **Kunskap och förståelse **    Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E201" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>ASA28A</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik i vård och omsorg utifrån persp…</t>
-        </is>
-      </c>
-      <c r="E202" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA28A</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>ASA28Q</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E203" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA28Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>ASA293</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E204" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA293</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>ASA2BA</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E205" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA2BA</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>GSA24U</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E206" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
-        <is>
-          <t>GSA24V</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kunskap och förståelse  Den studerande ska efter avslutad kurs kunna:…</t>
-        </is>
-      </c>
-      <c r="E207" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>GSA27Y</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna visa grundläggande kunskaper om:…</t>
-        </is>
-      </c>
-      <c r="E208" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
-        <is>
-          <t>GSA2AF</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E209" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>GSA2BV</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: unskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E210" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>GSA2DW</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
-        </is>
-      </c>
-      <c r="E211" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>GSA2E3</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E212" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
-        <is>
-          <t>GSA2E4</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E213" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>GSA2E5</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kunskap och förståelse        Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E214" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>GSA2GZ</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E215" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>GSA2NA</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E216" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
-        <is>
-          <t>GSA2NC</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: **Moment 1. Campusförlagd utbildning, 5 högskolepoäng**  Kunskap och förståelse    Efter avslutat moment ska den studera…</t>
-        </is>
-      </c>
-      <c r="E217" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>GSA2RE</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: **Kunskap och förståelse**    Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E218" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>GSA2SD</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: **Kunskap och förståelse**   Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E219" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>GSA2SE</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: **Kunskap och förståelse   **Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E220" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>GSA32Y</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E221" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>GSA352</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E222" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA352</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>GSA3AS</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E223" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>GSA3DM</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
-        </is>
-      </c>
-      <c r="E224" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>GSA3DN</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E225" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>GSA3DP</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E226" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DP</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>GSA3DQ</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E227" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>GSA3DR</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E228" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DR</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>GSA3DS</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E229" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>GSA3FK</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E230" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>GSA3FL</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: **Modul 1. Campusförlagd utbildning, 4,5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunn…</t>
-        </is>
-      </c>
-      <c r="E231" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
-        <is>
-          <t>GSA3HA</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E232" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
-        <is>
-          <t>SA1032</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E233" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1032</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>SA1037</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripandemål är att studenten inhämtat kunskap om teoretisk grund och evidensbas för återfallsprevention samt…</t>
-        </is>
-      </c>
-      <c r="E234" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
-        <is>
-          <t>SA1040</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska tillägna sig kunskaper inom Motiverande samtal (MI) med inriktning på…</t>
-        </is>
-      </c>
-      <c r="E235" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>SA1045</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E236" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>SA1046</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E237" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>SA1048</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
-        </is>
-      </c>
-      <c r="E238" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>SA2020</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att studenten skall ha fördjupat sina kunskaper om vetenskaplig metod, evidens och utvärderi…</t>
-        </is>
-      </c>
-      <c r="E239" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>SA3008</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse_  Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E240" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>ASR22N</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska kunna identifiera barnmorskelärarens roll i att planera och genomföra…</t>
-        </is>
-      </c>
-      <c r="E241" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>ASR24V</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E242" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
-        <is>
-          <t>ASR24W</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E243" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
-        <is>
-          <t>ASR24X</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E244" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
-        <is>
-          <t>ASR25P</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid okomplicerad graviditet, förlossning…</t>
-        </is>
-      </c>
-      <c r="E245" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>ASR25Q</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid komplicerad graviditet, förlossning …</t>
-        </is>
-      </c>
-      <c r="E246" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>ASR25T</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E247" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25T</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>ASR25U</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E248" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>ASR25V</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande självständigt kunna:…</t>
-        </is>
-      </c>
-      <c r="E249" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>ASR26N</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E250" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
-        <is>
-          <t>ASR26S</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid komplicerad graviditet, förlossning …</t>
-        </is>
-      </c>
-      <c r="E251" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
-        <is>
-          <t>ASR284</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
-        </is>
-      </c>
-      <c r="E252" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
-        <is>
-          <t>ASR285</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
-        </is>
-      </c>
-      <c r="E253" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>ASR286</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
-        </is>
-      </c>
-      <c r="E254" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>ASR296</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
-        </is>
-      </c>
-      <c r="E255" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR296</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>ASR29S</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter godkänd kurs ska studenten självständigt kunna…</t>
-        </is>
-      </c>
-      <c r="E256" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
-        <is>
-          <t>ASR29T</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E257" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>ASR29U</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter godkänd kurs ska studenten självständigt kunna:…</t>
-        </is>
-      </c>
-      <c r="E258" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="inlineStr">
-        <is>
-          <t>ASR29V</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter godkänd kurs ska studenten på en fördjupad nivå kunna:…</t>
-        </is>
-      </c>
-      <c r="E259" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
-        <is>
-          <t>ASR29W</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E260" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="2" t="inlineStr">
-        <is>
-          <t>ASR2AD</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E261" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="2" t="inlineStr">
-        <is>
-          <t>ASR2B9</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E262" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2B9</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
-        <is>
-          <t>ASR2BM</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E263" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2BM</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="2" t="inlineStr">
-        <is>
-          <t>ASR2CE</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E264" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CE</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="2" t="inlineStr">
-        <is>
-          <t>ASR2CF</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E265" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CF</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="2" t="inlineStr">
-        <is>
-          <t>ASR2CG</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E266" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CG</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="2" t="inlineStr">
-        <is>
-          <t>ASR2CH</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter godkänd kurs ska studenten självständigt kunna:…</t>
-        </is>
-      </c>
-      <c r="E267" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CH</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
-        <is>
-          <t>ASR2CJ</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E268" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="2" t="inlineStr">
-        <is>
-          <t>ASR2CK</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E269" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CK</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="2" t="inlineStr">
-        <is>
-          <t>GSR2A5</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna…</t>
-        </is>
-      </c>
-      <c r="E270" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="2" t="inlineStr">
-        <is>
-          <t>GSR2KZ</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E271" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="2" t="inlineStr">
-        <is>
-          <t>GSR2ZH</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E272" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2ZH</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="2" t="inlineStr">
-        <is>
-          <t>GSR38B</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E273" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
-        <is>
-          <t>GSR3BZ</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E274" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR3BZ</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
-        <is>
-          <t>SR3001</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska fördjupa och integrera kunskaper om barnmorskans arbetsfält och ansva…</t>
-        </is>
-      </c>
-      <c r="E275" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="2" t="inlineStr">
-        <is>
-          <t>SR3002</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om kvalitativa och kvantitativa metoder, utve…</t>
-        </is>
-      </c>
-      <c r="E276" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="2" t="inlineStr">
-        <is>
-          <t>SR3003</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska utveckla fördjupad förståelse för global sexuell och reproduktiv häls…</t>
-        </is>
-      </c>
-      <c r="E277" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="2" t="inlineStr">
-        <is>
-          <t>SR3004</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska kunna utveckla och tillämpa ett i praktiken hållbart vetenskapligt fö…</t>
-        </is>
-      </c>
-      <c r="E278" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="2" t="inlineStr">
-        <is>
-          <t>SR3005</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska visa fördjupade kunskaper om barnmorskans arbetsfält och ansvarsområd…</t>
-        </is>
-      </c>
-      <c r="E279" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="2" t="inlineStr">
-        <is>
-          <t>SR3006</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska visa fördjupade metodkunskaper och fördjupad förmåga att integrera ku…</t>
-        </is>
-      </c>
-      <c r="E280" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="2" t="inlineStr">
-        <is>
-          <t>SR3007</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska kunna visa fördjupade metodkunskaper och förmåga att integrera kunska…</t>
-        </is>
-      </c>
-      <c r="E281" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="2" t="inlineStr">
-        <is>
-          <t>SR3008</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska tillägna sig kunskaper om barnmorskans arbetsfält och ansvarsområde. …</t>
-        </is>
-      </c>
-      <c r="E282" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="2" t="inlineStr">
-        <is>
-          <t>SR3009</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om sexuell och reproduktiv hälsa som en mänsk…</t>
-        </is>
-      </c>
-      <c r="E283" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="2" t="inlineStr">
-        <is>
-          <t>SR3010</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripade mål är att den studerande ska förstå förlopp och processer vid normal och komplicerad graviditet, fö…</t>
-        </is>
-      </c>
-      <c r="E284" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="2" t="inlineStr">
-        <is>
-          <t>SR3011</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
-        </is>
-      </c>
-      <c r="E285" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="2" t="inlineStr">
-        <is>
-          <t>SR3012</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
-        </is>
-      </c>
-      <c r="E286" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="2" t="inlineStr">
-        <is>
-          <t>SR3013</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
-        </is>
-      </c>
-      <c r="E287" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="2" t="inlineStr">
-        <is>
-          <t>SR3014</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursen övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt kan tillämpa, ytt…</t>
-        </is>
-      </c>
-      <c r="E288" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="2" t="inlineStr">
-        <is>
-          <t>SR3015</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt ska fördjupa och…</t>
-        </is>
-      </c>
-      <c r="E289" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="2" t="inlineStr">
-        <is>
-          <t>AVV26K</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E290" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="2" t="inlineStr">
-        <is>
-          <t>AVV2A6</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E291" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="2" t="inlineStr">
-        <is>
-          <t>GVV3JJ</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E292" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVV3JJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="2" t="inlineStr">
-        <is>
-          <t>GVV3JK</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E293" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVV3JK</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="2" t="inlineStr">
-        <is>
-          <t>VV2001</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att studenten tillägnar sig kunskaper om handledning och handledningssituationer som är spec…</t>
-        </is>
-      </c>
-      <c r="E294" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="2" t="inlineStr">
-        <is>
-          <t>VV2002</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E295" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="2" t="inlineStr">
-        <is>
-          <t>VV3003</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E296" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3003</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="2" t="inlineStr">
-        <is>
-          <t>VV3006</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: **Kunskap och förståelse**   Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E297" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="2" t="inlineStr">
-        <is>
-          <t>VV3007</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: **Kunskap och förståelse**   Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E298" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3007</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="2" t="inlineStr">
-        <is>
-          <t>VV3009</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: **Kunskap och förståelse   **Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E299" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="2" t="inlineStr">
-        <is>
-          <t>VV3010</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
-        </is>
-      </c>
-      <c r="E300" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3010</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="2" t="inlineStr">
-        <is>
-          <t>VV3012</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap …</t>
-        </is>
-      </c>
-      <c r="E301" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="2" t="inlineStr">
-        <is>
-          <t>VV3014</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
-        </is>
-      </c>
-      <c r="E302" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="2" t="inlineStr">
-        <is>
-          <t>VV3015</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
-        </is>
-      </c>
-      <c r="E303" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>VV3017</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap,…</t>
-        </is>
-      </c>
-      <c r="E304" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E304"/>
+  <autoFilter ref="A1:E200"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -9051,214 +6243,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A208" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A211" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A212" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A213" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A214" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A215" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A216" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A217" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A218" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A219" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A221" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A222" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A223" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A224" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A226" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A227" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A228" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A229" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A230" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A231" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A232" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A233" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A234" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A235" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A236" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A237" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A238" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A239" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A240" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A241" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A242" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A243" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A244" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A245" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A246" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A247" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A248" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A249" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A250" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A251" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A252" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A253" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A254" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A255" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E255" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A256" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A257" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A258" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E258" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A259" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A260" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A261" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A262" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A263" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E263" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A264" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A265" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A266" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A267" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A268" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A269" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E269" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A270" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E270" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A271" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A272" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A273" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A274" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A275" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A276" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E276" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A277" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E277" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A278" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E278" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A279" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E279" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A280" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A281" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A282" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A283" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A284" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A285" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A286" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A287" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A288" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A289" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A290" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E290" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A291" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E291" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A292" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E292" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A293" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A294" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A295" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A296" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A297" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A298" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A299" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A300" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A301" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E301" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A302" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E302" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A303" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A304" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId606"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E200"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna redogöra för:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna redogöra för:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GIH35B</t>
+          <t>GIH2XY</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande på en fördjupad nivå kunna:…</t>
+          <t>Efter godkänd kurs ska studenten:…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2XY</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GIH35W</t>
+          <t>GIH35B</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande på en fördjupad nivå kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande på en fördjupad nivå kunna:…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GIH37N</t>
+          <t>GIH35W</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,19 +1540,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
+          <t>Efter godkänd kurs ska den studerande på en fördjupad nivå kunna:…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35W</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GIH37P</t>
+          <t>GIH392</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.   ### Delkurser  1…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH392</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH394</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH394</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GIH37R</t>
+          <t>GIH3AM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1621,19 +1621,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande, utifrån den kunskapsbas som lagts i Idrott och hälsa I med didaktisk inr…</t>
+          <t>Efter godkänd kurs ska studenten på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GIH37S</t>
+          <t>GIH3D4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper i idrotts- och hälsovetenskap med foku…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GIH392</t>
+          <t>GIH3D5</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH392</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GIH394</t>
+          <t>GIH3D6</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH394</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GIH3AM</t>
+          <t>GIH3GA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten på en grundläggande nivå kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande på en fördjupad nivå kunna:…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GIH3AN</t>
+          <t>IH1003</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.   ### Delkurser  1…</t>
+          <t>Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1003</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>IH1004</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
+          <t>Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1004</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GIH3D4</t>
+          <t>IH1006</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1815,14 +1815,14 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1006</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GIH3D5</t>
+          <t>IH1007</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1007</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GIH3D6</t>
+          <t>IH1008</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1869,14 +1869,14 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1008</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GIH3GA</t>
+          <t>IH1009</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1891,19 +1891,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande på en fördjupad nivå kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1009</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>IH1001</t>
+          <t>IH1010</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Kursen består av fyra delkurser med mål enligt nedanstående.  ### Delkurser  1.Motorik, anatomi och fysiologi I, 7,5 hög…</t>
+          <t>Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1010</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>IH1002</t>
+          <t>IH1011</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Kursen består av fyra delkurser med mål enligt nedanstående.  ### Delkurser  1.Motorik, anatomi och fysiologi II, 7,5 hö…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>IH1003</t>
+          <t>IH1012</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>IH1004</t>
+          <t>IH1015</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1999,19 +1999,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1015</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>IH1005</t>
+          <t>IH1023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande tillägnar sig kunskaper om rörelse som eget kunskapsområde och som medel …</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1023</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>IH1006</t>
+          <t>IH1024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2058,14 +2058,14 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1024</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>IH1007</t>
+          <t>IH1025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1025</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>IH1008</t>
+          <t>IH1026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2112,14 +2112,14 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>IH1009</t>
+          <t>IH1095</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>IH1010</t>
+          <t>IH1096</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2161,19 +2161,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>IH1011</t>
+          <t>IH1097</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>IH1012</t>
+          <t>IH1098</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>IH1015</t>
+          <t>IH1099</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2247,14 +2247,14 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>IH1020</t>
+          <t>IH1100</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande tillägnar sig kunskaper om och förståelse för humanbiologiska och socialp…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>IH1023</t>
+          <t>IH1101</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2301,14 +2301,14 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>IH1024</t>
+          <t>IH1102</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2328,14 +2328,14 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>IH1025</t>
+          <t>IH1113</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2355,14 +2355,14 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>IH1026</t>
+          <t>IH1114</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2382,14 +2382,14 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>IH1029</t>
+          <t>IH1122</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>### Delkurser  1.Idrott och hälsa - ett ämne för alla?, 15 högskolepoäng  Efter avslutad delkurs skall den studerande ku…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1122</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>IH1062</t>
+          <t>IH1130</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande tillägnar sig kunskaper och förståelse för fysiologiska och motivationsps…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>IH1082</t>
+          <t>IH2001</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2458,19 +2458,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Studenten ska efter genomförd kurs kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1082</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>IH1095</t>
+          <t>IH2003</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2003</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>IH1096</t>
+          <t>IH2004</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2004</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>IH1097</t>
+          <t>IH2005</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>IH1098</t>
+          <t>IH2006</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2006</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>IH1099</t>
+          <t>IH3007</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2598,19 +2598,19 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH3007</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>IH1100</t>
+          <t>AMC243</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2625,19 +2625,19 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>IH1101</t>
+          <t>AMC24R</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>IH1102</t>
+          <t>AMC25W</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC25W</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>IH1111</t>
+          <t>AMC265</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Studenten ska efter genomförd kurs kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1111</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>IH1113</t>
+          <t>AMC2BG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>IH1114</t>
+          <t>GMC2AH</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2760,19 +2760,19 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2AH</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>IH1122</t>
+          <t>GMC2M2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1122</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>IH1130</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2814,19 +2814,19 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>IH2001</t>
+          <t>MC2020</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande på ett professionellt, systematiskt och självständigt sätt och utifrån en helhets…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2020</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>IH2002</t>
+          <t>MC3027</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>### Delkurser  1.Träningslära, 7,5 högskolepoäng  Efter avslutad delkurs skall den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>IH2003</t>
+          <t>PS1018</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>PSA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PS1018</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>IH2004</t>
+          <t>GSA2GZ</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>IH2005</t>
+          <t>SA1032</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1032</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>IH2006</t>
+          <t>SA1046</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>IH3007</t>
+          <t>ASR24V</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3003,19 +3003,19 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>BKE223</t>
+          <t>ASR24W</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>KEA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om kemi.  Efter avslutad kurs…</t>
+          <t>Efter avslutad kurs ska…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BKE223</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>AMC22C</t>
+          <t>ASR24X</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Den studerande ska efter genomgången kurs självständigt kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC22C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>AMC243</t>
+          <t>ASR25T</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3084,19 +3084,19 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25T</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>AMC24R</t>
+          <t>ASR25U</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
+          <t>Efter avslutad kurs ska…</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>AMC25W</t>
+          <t>ASR25V</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
+          <t>Efter avslutad kurs ska den…</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC25W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>AMC265</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3165,19 +3165,19 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>AMC2BG</t>
+          <t>ASR29S</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande självständigt kunna:…</t>
+          <t>Efter godkänd kurs ska studenten självständigt kunna…</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GMC22H</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande ska ha kunskap om byggnad och funktion hos den friska människokroppen.  E…</t>
+          <t>Efter godkänd kurs ska studenten självständigt kunna:…</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GMC2AH</t>
+          <t>ASR29V</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten på en fördjupad nivå kunna:…</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GMC2M2</t>
+          <t>ASR2CH</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten självständigt kunna:…</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CH</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>MC1072</t>
+          <t>GSR2A5</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att studenten ska ha kunskap om byggnad och funktion hos den friska människokroppen.    Efte…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>MC1077</t>
+          <t>GSR2KZ</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att studenten ska ha kunskaper inom klinisk mikrobiologi, allmän farmakologi och läkemedelsh…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>MC1079</t>
+          <t>AVV26K</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande ska tillägna sig grundläggande kunskaper inom allmän farmakologi, läkemed…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>MC2017</t>
+          <t>VV2002</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>MC3027</t>
+          <t>VV3003</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3403,2447 +3403,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>GNV2KY</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>NAV</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper i och om naturvetenskap och teknik rele…</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>NV1024</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>NAV</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Det övergripande syftet med denna kurs är att kursdeltagarna ska utveckla sin didaktiska medvetenhet och praktiska skick…</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1024</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>NV1027</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>NAV</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att deltagarna utvecklar kunskap om och förmåga att arbeta med hållbar utveckling.    Efter …</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1027</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>NV1035</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>NAV</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om naturorienterande ämnen oc…</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>NV3001</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>NAV</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att kursdeltagaren ska utveckla kunskaper och förhållningssätt som ökar förutsättningarna fö…</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>PS1018</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>PSA</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PS1018</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>ASA24J</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>ASA24K</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna…</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>ASA24L</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande under kursen ska tillägna sig fördjupade kunskaper om barn och ungas utve…</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>ASA24M</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik i vård och omsorg utifrån persp…</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>ASA24N</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att studenten ska uppnå en bredare och djupare kompetens om äldre personer och åldrande utif…</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>ASA266</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Kunskap och förståelse   Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>ASA26U</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Kunskap och förståelse  Efter avslutad kurs ska den studerande självständigt kunna:…</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>ASA27E</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>**Kunskap och förståelse **    Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>ASA28A</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik i vård och omsorg utifrån persp…</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA28A</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>GSA24U</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>GSA24V</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Kunskap och förståelse  Den studerande ska efter avslutad kurs kunna:…</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>GSA27Y</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna visa grundläggande kunskaper om:…</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>GSA2AF</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>GSA2BV</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>unskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>GSA2DW</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>GSA2E3</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>GSA2E4</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>GSA2E5</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Kunskap och förståelse        Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>GSA2GZ</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>GSA2NA</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>GSA2NC</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>**Moment 1. Campusförlagd utbildning, 5 högskolepoäng**  Kunskap och förståelse    Efter avslutat moment ska den studera…</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>GSA2RE</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>**Kunskap och förståelse**    Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>GSA2SD</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>**Kunskap och förståelse**   Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>GSA2SE</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>**Kunskap och förståelse   **Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>GSA32Y</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>**Modul 1. Campusförlagd utbildning, 5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>GSA3DM</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>GSA3DS</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>**Modul 1. Campusförlagd utbildning, 5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>GSA3FL</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>**Modul 1. Campusförlagd utbildning, 4,5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunn…</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>SA1032</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1032</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>SA1037</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Kursens övergripandemål är att studenten inhämtat kunskap om teoretisk grund och evidensbas för återfallsprevention samt…</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>SA1040</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska tillägna sig kunskaper inom Motiverande samtal (MI) med inriktning på…</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>SA1045</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>SA1046</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>SA1048</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>SA2020</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att studenten skall ha fördjupat sina kunskaper om vetenskaplig metod, evidens och utvärderi…</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>SA3008</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>_Kunskap och förståelse_  Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>ASR22N</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska kunna identifiera barnmorskelärarens roll i att planera och genomföra…</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>ASR24V</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>ASR24W</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>ASR24X</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>ASR25P</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid okomplicerad graviditet, förlossning…</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>ASR25Q</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid komplicerad graviditet, förlossning …</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>ASR25T</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25T</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>ASR25U</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>ASR25V</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>ASR26N</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>ASR26S</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid komplicerad graviditet, förlossning …</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>ASR284</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>ASR285</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>ASR286</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>ASR296</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR296</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>ASR29S</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska studenten självständigt kunna…</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>ASR29U</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska studenten självständigt kunna:…</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>ASR29V</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska studenten på en fördjupad nivå kunna:…</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>ASR2CH</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska studenten självständigt kunna:…</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CH</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>GSR2A5</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
-        </is>
-      </c>
-      <c r="E172" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>GSR2KZ</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>SR3001</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska fördjupa och integrera kunskaper om barnmorskans arbetsfält och ansva…</t>
-        </is>
-      </c>
-      <c r="E174" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>SR3002</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om kvalitativa och kvantitativa metoder, utve…</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>SR3003</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska utveckla fördjupad förståelse för global sexuell och reproduktiv häls…</t>
-        </is>
-      </c>
-      <c r="E176" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
-        <is>
-          <t>SR3004</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska kunna utveckla och tillämpa ett i praktiken hållbart vetenskapligt fö…</t>
-        </is>
-      </c>
-      <c r="E177" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>SR3005</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska visa fördjupade kunskaper om barnmorskans arbetsfält och ansvarsområd…</t>
-        </is>
-      </c>
-      <c r="E178" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>SR3006</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska visa fördjupade metodkunskaper och fördjupad förmåga att integrera ku…</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>SR3007</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska kunna visa fördjupade metodkunskaper och förmåga att integrera kunska…</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
-        <is>
-          <t>SR3008</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska tillägna sig kunskaper om barnmorskans arbetsfält och ansvarsområde. …</t>
-        </is>
-      </c>
-      <c r="E181" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>SR3009</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om sexuell och reproduktiv hälsa som en mänsk…</t>
-        </is>
-      </c>
-      <c r="E182" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>SR3010</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>Kursens övergripade mål är att den studerande ska förstå förlopp och processer vid normal och komplicerad graviditet, fö…</t>
-        </is>
-      </c>
-      <c r="E183" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>SR3011</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
-        </is>
-      </c>
-      <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>SR3012</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
-        </is>
-      </c>
-      <c r="E185" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>SR3013</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
-        </is>
-      </c>
-      <c r="E186" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
-        <is>
-          <t>SR3014</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>Kursen övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt kan tillämpa, ytt…</t>
-        </is>
-      </c>
-      <c r="E187" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>SR3015</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt ska fördjupa och…</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
-        <is>
-          <t>AVV26K</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E189" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>VV2001</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att studenten tillägnar sig kunskaper om handledning och handledningssituationer som är spec…</t>
-        </is>
-      </c>
-      <c r="E190" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>VV2002</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E191" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>VV3003</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E192" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3003</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>VV3006</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>**Kunskap och förståelse**   Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E193" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>VV3007</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>**Kunskap och förståelse**   Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E194" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3007</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>VV3009</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>**Kunskap och förståelse   **Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E195" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>VV3010</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
-        </is>
-      </c>
-      <c r="E196" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3010</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>VV3012</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap …</t>
-        </is>
-      </c>
-      <c r="E197" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>VV3014</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
-        </is>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>VV3015</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
-        </is>
-      </c>
-      <c r="E199" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>VV3017</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap,…</t>
-        </is>
-      </c>
-      <c r="E200" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E200"/>
+  <autoFilter ref="A1:E110"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -6063,186 +3633,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2902,7 +2902,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GSA2GZ</t>
+          <t>ASA24J</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2922,14 +2922,14 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>SA1032</t>
+          <t>ASA24K</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2944,19 +2944,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>SA1046</t>
+          <t>ASA266</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2976,19 +2976,19 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>ASR24V</t>
+          <t>ASA26U</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>ASR24W</t>
+          <t>ASA27E</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>ASR24X</t>
+          <t>GSA24U</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3057,19 +3057,19 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>ASR25T</t>
+          <t>GSA27Y</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna visa grundläggande kunskaper om:…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>ASR25U</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>ASR25V</t>
+          <t>GSA2E3</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>ASR26N</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3165,19 +3165,19 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>ASR29S</t>
+          <t>GSA2E5</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten självständigt kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>ASR29U</t>
+          <t>GSA2GZ</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten självständigt kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>GSA2NA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten på en fördjupad nivå kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>ASR2CH</t>
+          <t>GSA2RE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten självständigt kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GSR2A5</t>
+          <t>GSA2SD</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GSR2KZ</t>
+          <t>SA1032</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3327,19 +3327,19 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1032</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>AVV26K</t>
+          <t>SA1045</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3354,19 +3354,19 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>VV2002</t>
+          <t>SA1046</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3376,44 +3376,557 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>SA3008</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>ASR24V</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>ASR24W</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska…</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>ASR24X</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>ASR25T</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25T</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>ASR25U</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska…</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>ASR25V</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den…</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>ASR26N</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>ASR29S</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Efter godkänd kurs ska studenten självständigt kunna…</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>ASR29U</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Efter godkänd kurs ska studenten självständigt kunna:…</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>ASR29V</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Efter godkänd kurs ska studenten på en fördjupad nivå kunna:…</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>ASR2CH</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Efter godkänd kurs ska studenten självständigt kunna:…</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CH</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>GSR2A5</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>GSR2KZ</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>AVV26K</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>AVV26M</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande, med tillämpning inom hälso- och sjukvård och socialt arbete kunna:…</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26M</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>VV2002</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
           <t>VV3003</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>VÅE</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3003</t>
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>VV3006</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>VV3007</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3007</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E110"/>
+  <autoFilter ref="A1:E129"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3633,6 +4146,44 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2902,7 +2902,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>ASA24J</t>
+          <t>GSA2GZ</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2922,14 +2922,14 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>ASA24K</t>
+          <t>SA1032</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2944,19 +2944,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1032</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>ASA266</t>
+          <t>SA1046</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2976,19 +2976,19 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>ASA26U</t>
+          <t>ASR24V</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>ASA27E</t>
+          <t>ASR24W</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GSA24U</t>
+          <t>ASR24X</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3057,19 +3057,19 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GSA27Y</t>
+          <t>ASR25T</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna visa grundläggande kunskaper om:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25T</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>ASR25U</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska…</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GSA2E3</t>
+          <t>ASR25V</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den…</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GSA2E4</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3165,19 +3165,19 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GSA2E5</t>
+          <t>ASR29S</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten självständigt kunna…</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GSA2GZ</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten självständigt kunna:…</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GSA2NA</t>
+          <t>ASR29V</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten på en fördjupad nivå kunna:…</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GSA2RE</t>
+          <t>ASR2CH</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten självständigt kunna:…</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CH</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GSA2SD</t>
+          <t>GSR2A5</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>SA1032</t>
+          <t>GSR2KZ</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3327,19 +3327,19 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>SA1045</t>
+          <t>AVV26K</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3354,19 +3354,19 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>SA1046</t>
+          <t>VV2002</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>SA3008</t>
+          <t>VV3003</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3408,525 +3408,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>ASR24V</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>ASR24W</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska…</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>ASR24X</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>ASR25T</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25T</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>ASR25U</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska…</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>ASR25V</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den…</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>ASR26N</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>ASR29S</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska studenten självständigt kunna…</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>ASR29U</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska studenten självständigt kunna:…</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>ASR29V</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska studenten på en fördjupad nivå kunna:…</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>ASR2CH</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska studenten självständigt kunna:…</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CH</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>GSR2A5</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>GSR2KZ</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>AVV26K</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>AVV26M</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande, med tillämpning inom hälso- och sjukvård och socialt arbete kunna:…</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26M</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>VV2002</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>VV3003</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3003</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>VV3006</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>VV3007</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3007</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E129"/>
+  <autoFilter ref="A1:E110"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -4146,44 +3633,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3412,8 +3412,35 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>FVV222H</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>VÅRDVETS</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska doktoranden kunna:…</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FVV222H</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E110"/>
+  <autoFilter ref="A1:E111"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3633,6 +3660,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3412,35 +3412,8 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>FVV222H</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>VÅRDVETS</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska doktoranden kunna:…</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FVV222H</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E111"/>
+  <autoFilter ref="A1:E110"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3660,8 +3633,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$G$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
         </is>
@@ -509,15 +527,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+          <t>2020-03-05</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
         </is>
@@ -536,15 +560,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+          <t>2018-09-11</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH24A</t>
         </is>
@@ -563,15 +593,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2A6</t>
         </is>
@@ -590,15 +626,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Efter…</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D4</t>
         </is>
@@ -617,15 +663,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2020-05-20</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Efter…</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D5</t>
         </is>
@@ -644,15 +700,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2020-05-26</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Efter…</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D6</t>
         </is>
@@ -671,15 +737,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2020-05-26</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Efter…</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D7</t>
         </is>
@@ -698,15 +774,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2020-05-28</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Efter…</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D8</t>
         </is>
@@ -725,15 +811,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2020-05-28</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Efter…</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D9</t>
         </is>
@@ -752,15 +848,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2020-05-28</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>Efter…</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DB</t>
         </is>
@@ -779,15 +885,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2020-05-28</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Efter…</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DC</t>
         </is>
@@ -806,15 +922,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Efter…</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
         </is>
@@ -833,15 +959,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>Efter…</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
         </is>
@@ -860,15 +996,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+          <t>2020-05-20</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
         </is>
@@ -887,15 +1033,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+          <t>2021-02-03</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LP</t>
         </is>
@@ -914,15 +1066,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
         </is>
@@ -941,15 +1099,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
         </is>
@@ -968,15 +1132,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+          <t>2021-02-15</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
         </is>
@@ -995,15 +1169,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
         </is>
@@ -1022,15 +1202,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
         </is>
@@ -1049,15 +1235,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+          <t>2021-02-15</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
         </is>
@@ -1076,15 +1272,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
         </is>
@@ -1103,15 +1305,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
         </is>
@@ -1130,15 +1338,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
         </is>
@@ -1157,15 +1371,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
         </is>
@@ -1184,15 +1404,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
+          <t>2021-06-07</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QK</t>
         </is>
@@ -1211,15 +1437,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
+          <t>2021-06-07</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
         </is>
@@ -1238,15 +1470,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
         </is>
@@ -1265,15 +1503,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
+          <t>2022-02-28</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
         </is>
@@ -1292,15 +1536,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
         </is>
@@ -1319,15 +1569,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
         </is>
@@ -1346,15 +1602,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
         </is>
@@ -1373,15 +1635,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WU</t>
         </is>
@@ -1400,15 +1668,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
         </is>
@@ -1427,15 +1701,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
         </is>
@@ -1454,15 +1734,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
         </is>
@@ -1481,15 +1771,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>2022-09-30</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>Efter godkänd kurs ska studenten:…</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2XY</t>
         </is>
@@ -1508,15 +1808,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande på en fördjupad nivå kunna:…</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
         </is>
@@ -1535,15 +1841,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande på en fördjupad nivå kunna:…</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35W</t>
         </is>
@@ -1562,15 +1874,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH392</t>
         </is>
@@ -1589,15 +1907,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH394</t>
         </is>
@@ -1616,15 +1940,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenten på en grundläggande nivå kunna:…</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
         </is>
@@ -1643,15 +1973,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
         </is>
@@ -1670,15 +2006,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
         </is>
@@ -1697,15 +2039,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
         </is>
@@ -1724,15 +2072,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande på en fördjupad nivå kunna:…</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
         </is>
@@ -1751,15 +2105,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1003</t>
         </is>
@@ -1778,15 +2138,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1004</t>
         </is>
@@ -1805,15 +2171,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1006</t>
         </is>
@@ -1832,15 +2204,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1007</t>
         </is>
@@ -1859,15 +2237,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1008</t>
         </is>
@@ -1886,15 +2270,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1009</t>
         </is>
@@ -1913,15 +2303,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1010</t>
         </is>
@@ -1940,15 +2336,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
         </is>
@@ -1967,15 +2369,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
         </is>
@@ -1994,15 +2402,25 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1015</t>
         </is>
@@ -2021,15 +2439,25 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
+          <t>2012-10-31</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1023</t>
         </is>
@@ -2048,15 +2476,25 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
+          <t>2012-10-31</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1024</t>
         </is>
@@ -2075,15 +2513,25 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
+          <t>2012-10-31</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1025</t>
         </is>
@@ -2102,15 +2550,25 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
+          <t>2012-10-31</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1026</t>
         </is>
@@ -2129,15 +2587,21 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
         </is>
@@ -2156,15 +2620,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
         </is>
@@ -2183,15 +2653,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
         </is>
@@ -2210,15 +2686,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
         </is>
@@ -2237,15 +2719,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
         </is>
@@ -2264,15 +2752,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
         </is>
@@ -2291,15 +2785,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
         </is>
@@ -2318,15 +2818,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
         </is>
@@ -2345,15 +2851,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
         </is>
@@ -2372,15 +2884,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
         </is>
@@ -2399,15 +2917,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+          <t>2016-08-26</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1122</t>
         </is>
@@ -2426,15 +2950,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
+          <t>2017-08-24</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
         </is>
@@ -2453,15 +2983,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
         </is>
@@ -2480,15 +3016,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2003</t>
         </is>
@@ -2507,15 +3049,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2004</t>
         </is>
@@ -2534,15 +3082,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
         </is>
@@ -2561,15 +3115,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall den studerande kunna…</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2006</t>
         </is>
@@ -2588,15 +3148,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
+          <t>2012-04-11</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH3007</t>
         </is>
@@ -2615,15 +3181,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
+          <t>2020-02-20</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
         </is>
@@ -2642,15 +3214,25 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
         </is>
@@ -2669,15 +3251,25 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC25W</t>
         </is>
@@ -2696,15 +3288,25 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
         </is>
@@ -2723,15 +3325,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
         </is>
@@ -2750,15 +3358,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2AH</t>
         </is>
@@ -2777,15 +3391,25 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
         </is>
@@ -2804,15 +3428,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
@@ -2831,15 +3461,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
+          <t>2014-03-20</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande på ett professionellt, systematiskt och självständigt sätt och utifrån en helhets…</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2020</t>
         </is>
@@ -2858,15 +3494,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
         </is>
@@ -2885,15 +3527,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+          <t>2016-03-10</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PS1018</t>
         </is>
@@ -2912,15 +3560,25 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
         </is>
@@ -2939,15 +3597,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
+          <t>2014-10-14</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1032</t>
         </is>
@@ -2966,15 +3630,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
+          <t>2017-11-30</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
         </is>
@@ -2993,15 +3663,25 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
@@ -3020,15 +3700,25 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska…</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
         </is>
@@ -3047,15 +3737,25 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+          <t>2020-05-26</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
         </is>
@@ -3074,15 +3774,25 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25T</t>
         </is>
@@ -3101,15 +3811,25 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska…</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
         </is>
@@ -3128,15 +3848,25 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den…</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
         </is>
@@ -3155,15 +3885,25 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
+          <t>2021-03-03</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
@@ -3182,15 +3922,21 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenten självständigt kunna…</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
         </is>
@@ -3209,15 +3955,21 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenten självständigt kunna:…</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
@@ -3236,15 +3988,21 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenten på en fördjupad nivå kunna:…</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
@@ -3263,15 +4021,21 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenten självständigt kunna:…</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CH</t>
         </is>
@@ -3290,15 +4054,25 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2019-06-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t>2021-02-19</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
         </is>
@@ -3317,15 +4091,25 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
+          <t>2020-12-10</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
         </is>
@@ -3344,15 +4128,25 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
+          <t>2021-03-02</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
         </is>
@@ -3371,15 +4165,25 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t>2012-03-05</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
         </is>
@@ -3398,241 +4202,247 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
+          <t>2008-03-03</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3003</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E110"/>
+  <autoFilter ref="A1:G110"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId208"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId212"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId218"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens.xlsx
@@ -863,7 +863,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Efter…</t>
+          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Efter…</t>
+          <t>Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:…</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
